--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -240,7 +240,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t>2026-09-29T07:24:05.324856+05:30</t>
+          <t>2026-09-29T07:25:28.957582+05:30</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -240,7 +240,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t>2026-10-02T12:04:37.491963+05:30</t>
+          <t>2026-10-03T10:14:16.667091+05:30</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -240,7 +240,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t>2026-10-03T10:14:16.667091+05:30</t>
+          <t>2026-10-03T10:46:41.154814+05:30</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -240,7 +240,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t>2026-10-03T10:46:41.154814+05:30</t>
+          <t>2026-10-04T00:10:21.852985+05:30</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -240,7 +240,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t>2026-10-04T00:10:21.852985+05:30</t>
+          <t>2026-10-03T10:46:41.154814+05:30</t>
         </is>
       </c>
       <c t="inlineStr">
